--- a/TestData/Register_Data.xlsx
+++ b/TestData/Register_Data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29721"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B072BD1-2EF6-4C3C-BECB-51E902EDBD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1EB8B495-F60F-4DB0-BEB8-372919975BBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
   <si>
     <t>First Name</t>
   </si>
@@ -73,6 +79,9 @@
   </si>
   <si>
     <t>SSN</t>
+  </si>
+  <si>
+    <t>258963147</t>
   </si>
 </sst>
 </file>
@@ -433,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -447,7 +456,6 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
@@ -456,6 +464,7 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
@@ -485,24 +494,32 @@
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="2">
-        <v>100012</v>
+      <c r="B6" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
         <v>12</v>
+      </c>
+      <c r="B7" s="2">
+        <v>100012</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="2">
-        <v>258963147</v>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
